--- a/04-northbridge-cloudworks-grc-program/04-control-framework-crosswalk/artifacts/Northbridge-Control-Framework-Crosswalk-and-Testing.xlsx
+++ b/04-northbridge-cloudworks-grc-program/04-control-framework-crosswalk/artifacts/Northbridge-Control-Framework-Crosswalk-and-Testing.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Test Workpapers'!$A$1:$J$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Findings'!$A$1:$H$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Evidence Requests'!$A$1:$F$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'References'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'References'!$A$1:$C$12</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -239,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -799,7 +805,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Controls</t>
@@ -819,9 +825,9 @@
           <t>Control Count</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>High Risk</t>
+      <c r="F3" s="35" t="inlineStr">
+        <is>
+          <t>High Criticality</t>
         </is>
       </c>
       <c r="G3" s="28" t="inlineStr">
@@ -970,7 +976,7 @@
         </is>
       </c>
       <c r="B8" s="34" t="n">
-        <v>46247</v>
+        <v>46267</v>
       </c>
       <c r="D8" s="31" t="inlineStr">
         <is>
@@ -1057,7 +1063,7 @@
     <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Control ID</t>
@@ -1113,9 +1119,9 @@
           <t>SOC 2</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
-        <is>
-          <t>Risk Tier</t>
+      <c r="L1" s="36" t="inlineStr">
+        <is>
+          <t>Control Criticality</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4032,6 +4038,23 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Scenario dates and rating definitions</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>Fictional assessment assumptions; see shared company profile</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>../../00-company-profile/Northbridge-Company-and-GRC-Scope.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
